--- a/src/main/webapp/xlsxTemplates/物料导入示例模板.xlsx
+++ b/src/main/webapp/xlsxTemplates/物料导入示例模板.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1100404113" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,30 +27,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
-    <t>产品编号</t>
-  </si>
-  <si>
-    <t>产品单位</t>
-  </si>
-  <si>
-    <t>产品数量</t>
-  </si>
-  <si>
-    <t>计划单价</t>
-  </si>
-  <si>
-    <t>计划总价</t>
-  </si>
-  <si>
-    <t>销售单价</t>
-  </si>
-  <si>
-    <t>销售总价</t>
+    <t>订货型号</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>总价</t>
   </si>
   <si>
     <t>单重</t>
@@ -59,6 +56,9 @@
     <t>总重</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>行订单号</t>
   </si>
   <si>
@@ -66,21 +66,6 @@
   </si>
   <si>
     <t>国网物料编码</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>重锤螺丝</t>
-  </si>
-  <si>
-    <t>BJM18*595</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>测试</t>
   </si>
 </sst>
 </file>
@@ -93,7 +78,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,7 +87,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -251,8 +243,15 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +260,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -446,12 +451,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -553,170 +588,180 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -766,222 +811,9 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1240,21 +1072,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="17.75" customWidth="1"/>
-    <col min="2" max="2" width="15.125" customWidth="1"/>
-    <col min="3" max="3" width="11.875" customWidth="1"/>
-    <col min="12" max="12" width="29.125" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="1" max="1" width="6.15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.8833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.3416666666667" style="1" customWidth="1"/>
+    <col min="4" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="10.375" style="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="9.375" style="1"/>
+    <col min="10" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="19.125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1" customHeight="1" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1263,83 +1100,52 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1</v>
-      </c>
-      <c r="J2" s="1">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1</v>
-      </c>
-      <c r="M2" s="1">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>